--- a/rules/sources/sec.nport.security/MAPPING.xlsx
+++ b/rules/sources/sec.nport.security/MAPPING.xlsx
@@ -1079,16 +1079,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="51" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1125,6 +1125,80 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_name_of_issuer</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>The value is not a placeholder: NONE, NULL, UNKNOWN, TBD, NOTAPPLICABLE, NOTAVAILABLE</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>fields.name_of_issuer</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Withheld: kept on the record, never used to match</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>quality.sec.nport.security.v1.checks[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>placeholder_name_of_issuer</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>The value is not a placeholder: NONE, NULL, UNKNOWN, TBD, NOTAPPLICABLE, NOTAVAILABLE</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>fields.name_of_issuer</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Withheld: kept on the record, never used to match</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>quality.sec.nport.security_isin.v1.checks[0]</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1506,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/sources/sec.nport.security/MAPPING.xlsx
+++ b/rules/sources/sec.nport.security/MAPPING.xlsx
@@ -638,14 +638,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -768,56 +768,64 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security_isin.v1</t>
+          <t>sec.nport.security.v1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
+          <t>relationship ISSUED_BY</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>name.name_sample (lines)</t>
+          <t>item.issuer_lei</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>MDM field</t>
+          <t>Link to gleif.level1.v1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
+          <t>mdm.sec.nport.security.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security_isin.v1</t>
+          <t>sec.nport.security.v1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>title_of_class</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
+          <t>relationship ISSUED_BY</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>title.title_sample (lines)</t>
+          <t>issuer</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>MDM field</t>
+          <t>One link per item (item.)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.title_of_class</t>
+          <t>mdm.sec.nport.security.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
@@ -829,21 +837,77 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>issuer_lei</t>
+          <t>name_of_issuer</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>name.name_sample (lines)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>title_of_class</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>title.title_sample (lines)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.title_of_class</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>issuer_lei</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>lei.lei_sample (lines)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>MDM field</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>mdm.sec.nport.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.issuer_lei</t>
         </is>

--- a/rules/sources/sec.nport.security/MAPPING.xlsx
+++ b/rules/sources/sec.nport.security/MAPPING.xlsx
@@ -638,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -910,6 +910,70 @@
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>mdm.sec.nport.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.issuer_lei</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>relationship ISSUED_BY</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>item.issuer_lei</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Link to gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security_isin.v1.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>relationship ISSUED_BY</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>issuer</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>One link per item (item.)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security_isin.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>

--- a/rules/sources/sec.nport.security/MAPPING.xlsx
+++ b/rules/sources/sec.nport.security/MAPPING.xlsx
@@ -1347,7 +1347,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
+          <t>sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
+          <t>sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">

--- a/rules/sources/sec.nport.security/MAPPING.xlsx
+++ b/rules/sources/sec.nport.security/MAPPING.xlsx
@@ -428,10 +428,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="59" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -486,7 +486,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1: provider</t>
+          <t>sec.nport.security.v2: provider</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -498,7 +498,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1: kind</t>
+          <t>sec.nport.security.v2: kind</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -510,19 +510,19 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1: one record is</t>
+          <t>sec.nport.security.v2: one record is</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>the CUSIP, upper-cased; one record per CUSIP over the quarter</t>
+          <t>the CUSIP, upper-cased, else the ISIN of a holding with no usable CUSIP; one record per Security over the quarter</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1: one publication is</t>
+          <t>sec.nport.security.v2: one publication is</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1: a file covers</t>
+          <t>sec.nport.security.v2: a file covers</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -546,84 +546,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1: set aside without stopping the run</t>
+          <t>sec.nport.security.v2: set aside without stopping the run</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>invalid_cusip, invalid_cusip_checksum, invalid_isin, invalid_isin_checksum, missing_record_identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1: provider</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1: kind</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1: one record is</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>the ISIN, upper-cased; one record per ISIN of a holding with no usable CUSIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1: one publication is</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>the quarter's N-PORT data set file and the reduction and combine contracts</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1: a file covers</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>the Securities one quarter's holdings name; no retirement by absence</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1: set aside without stopping the run</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>invalid_isin, invalid_isin_checksum, missing_record_identity</t>
         </is>
       </c>
     </row>
@@ -638,10 +566,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
@@ -684,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -705,14 +633,14 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -733,14 +661,14 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.title_of_class</t>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.title_of_class</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -761,14 +689,14 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.issuer_lei</t>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.issuer_lei</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -793,14 +721,14 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security.v1.contract.adapter.relationships</t>
+          <t>mdm.sec.nport.security.v2.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -825,155 +753,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>name_of_issuer</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>name.name_sample (lines)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>MDM field</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>mdm.sec.nport.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name_of_issuer</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>title_of_class</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>title.title_sample (lines)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>MDM field</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>mdm.sec.nport.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.title_of_class</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>issuer_lei</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>lei.lei_sample (lines)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>MDM field</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>mdm.sec.nport.security_isin.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.issuer_lei</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>relationship ISSUED_BY</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>to</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>item.issuer_lei</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Link to gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>mdm.sec.nport.security_isin.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>relationship ISSUED_BY</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>each</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>issuer</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>One link per item (item.)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>mdm.sec.nport.security_isin.v1.contract.adapter.relationships</t>
+          <t>mdm.sec.nport.security.v2.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
@@ -988,10 +768,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1040,7 +820,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1070,14 +850,14 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security.v1.contract.adapter.identifiers.cusip</t>
+          <t>mdm.sec.nport.security.v2.contract.adapter.identifiers.cusip</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1107,44 +887,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security.v1.contract.adapter.identifiers.isin</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>isin</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>isin</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>isin</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Only with a new dataset code</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>mdm.sec.nport.security_isin.v1.contract.adapter.identifiers.isin</t>
+          <t>mdm.sec.nport.security.v2.contract.adapter.identifiers.isin</t>
         </is>
       </c>
     </row>
@@ -1207,16 +950,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="51" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1259,7 +1002,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1289,44 +1032,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>quality.sec.nport.security.v1.checks[0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>placeholder_name_of_issuer</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>The value is not a placeholder: NONE, NULL, UNKNOWN, TBD, NOTAPPLICABLE, NOTAVAILABLE</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>fields.name_of_issuer</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Withheld: kept on the record, never used to match</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>quality.sec.nport.security_isin.v1.checks[0]</t>
+          <t>quality.sec.nport.security.v2.checks[0]</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1397,12 +1103,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1, sec.nport.security_isin.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1429,7 +1135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1461,12 +1167,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1475,102 +1181,6 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>issuer_lei</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v1, sec.nport.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v1</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>name_of_issuer</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>title_of_class</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/sources/sec.nport.security/MAPPING.xlsx
+++ b/rules/sources/sec.nport.security/MAPPING.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -673,23 +673,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>issuer_lei</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
+          <t>relationship ISSUED_BY</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>lei.lei_sample (lines)</t>
+          <t>item.issuer_lei</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>MDM field</t>
+          <t>Link to gleif.level1.v1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.issuer_lei</t>
+          <t>mdm.sec.nport.security.v2.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
@@ -706,52 +710,20 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>each</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>item.issuer_lei</t>
+          <t>issuer</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Link to gleif.level1.v1</t>
+          <t>One link per item (item.)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>mdm.sec.nport.security.v2.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v2</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>relationship ISSUED_BY</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>each</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>issuer</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>One link per item (item.)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>mdm.sec.nport.security.v2.contract.adapter.relationships</t>
         </is>
@@ -1047,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1098,17 +1070,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>issuer_lei</t>
+          <t>name_of_issuer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1130,17 +1102,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>title_of_class</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1149,38 +1121,6 @@
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>title_of_class</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/sources/sec.nport.security/MAPPING.xlsx
+++ b/rules/sources/sec.nport.security/MAPPING.xlsx
@@ -566,13 +566,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
@@ -673,27 +673,23 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>relationship ISSUED_BY</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>to</t>
-        </is>
-      </c>
+          <t>share_class</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>item.issuer_lei</t>
+          <t>class (lines)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Link to gleif.level1.v1</t>
+          <t>MDM field</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security.v2.contract.adapter.relationships</t>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.share_class</t>
         </is>
       </c>
     </row>
@@ -705,25 +701,85 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>share_classes_filed</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>classes.class_sample (lines)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Matching only</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.share_classes_filed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>relationship ISSUED_BY</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>item.issuer_lei</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Link to gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security.v2.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>relationship ISSUED_BY</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>each</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>issuer</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>One link per item (item.)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>mdm.sec.nport.security.v2.contract.adapter.relationships</t>
         </is>
@@ -922,14 +978,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="51" customWidth="1" min="6" max="6"/>
     <col width="41" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1005,6 +1061,43 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>quality.sec.nport.security.v2.checks[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>share_class_one_letter</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>The value matches [A-Z]</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>matching.share_classes_filed</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Counted only</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>quality.sec.nport.security.v2.checks[1]</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1102,25 +1195,57 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>share_class</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>title_of_class</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>sec.nport.security.v2</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Kind default</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/sources/sec.nport.security/MAPPING.xlsx
+++ b/rules/sources/sec.nport.security/MAPPING.xlsx
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/rules/sources/sec.nport.security/MAPPING.xlsx
+++ b/rules/sources/sec.nport.security/MAPPING.xlsx
@@ -1118,7 +1118,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v3, sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">

--- a/rules/sources/sec.nport.security/MAPPING.xlsx
+++ b/rules/sources/sec.nport.security/MAPPING.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -701,23 +701,23 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>share_classes_filed</t>
+          <t>asset_category</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>classes.class_sample (lines)</t>
+          <t>asset_category</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Matching only</t>
+          <t>MDM field</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.share_classes_filed</t>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.asset_category</t>
         </is>
       </c>
     </row>
@@ -729,27 +729,23 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>relationship ISSUED_BY</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>to</t>
-        </is>
-      </c>
+          <t>issuer_type</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>item.issuer_lei</t>
+          <t>issuer_type</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Link to gleif.level1.v1</t>
+          <t>MDM field</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.nport.security.v2.contract.adapter.relationships</t>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.issuer_type</t>
         </is>
       </c>
     </row>
@@ -761,25 +757,197 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>investment_country</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>investment_country</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.investment_country</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>restricted</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>restricted</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.restricted</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>derivative_category</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>derivative_category</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.derivative_category</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>share_classes_filed</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>classes.class_sample (lines)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Matching only</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security.v2.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.share_classes_filed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>relationship ISSUED_BY</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>item.issuer_lei</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Link to gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>mdm.sec.nport.security.v2.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>relationship ISSUED_BY</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>each</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>issuer</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>One link per item (item.)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>mdm.sec.nport.security.v2.contract.adapter.relationships</t>
         </is>
@@ -1112,11 +1280,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1163,17 +1331,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>asset_category</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3, sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1195,17 +1363,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>share_class</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1227,25 +1395,217 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>derivative_category</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>investment_country</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>issuer_type</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3, sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>restricted</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>share_class</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>title_of_class</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Kind default</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/sources/sec.nport.security/MAPPING.xlsx
+++ b/rules/sources/sec.nport.security/MAPPING.xlsx
@@ -13,7 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critical data elements" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data quality" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Who wins" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline targets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline steps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1622,6 +1624,807 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Run checks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lease seconds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Heartbeat seconds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>manifest.hash, work.accounting, journal.delivered</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Requires</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>submissions</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>identifiers</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>holdings</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>identifiers</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>issuers</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>identifiers, submissions</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>source.combine</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>holdings</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.combined</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>issuer_reduce</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>source.combine</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>issuers</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.combined</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>combine</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>source.combine</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>reduce, issuer_reduce</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.combined</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>combine</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[7]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>registrants</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>submissions</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[8]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[9]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>identifiers, submissions, registrants, series</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[10]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>holding_combine</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>source.combine</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.combined</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[11]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>holding_rows</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>holding_combine</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>mdm.prepare</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, mdm.prepared</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[13]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>mdm.merge</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>{batch_id}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>mdm:consumer:{consumer}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, mdm.committed</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[14]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>processed</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>journal.record</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, journal.recorded</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[15]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
